--- a/Tools/Config/Datas/__tables__.xlsx
+++ b/Tools/Config/Datas/__tables__.xlsx
@@ -1242,6 +1242,16 @@
           <t>主动技能伤害倍率@AbilitySetting.xlsx</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SkillId+SegmentIndex</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="inlineStr">

--- a/Tools/Config/Datas/__tables__.xlsx
+++ b/Tools/Config/Datas/__tables__.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="28.5833333333333" customWidth="1" style="4" min="2" max="2"/>
@@ -1242,12 +1242,12 @@
           <t>主动技能伤害倍率@AbilitySetting.xlsx</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>SkillId+SegmentIndex</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>list</t>
         </is>
@@ -1330,6 +1330,26 @@
       <c r="E9" s="3" t="inlineStr">
         <is>
           <t>CharacterAttri@RoleAttri.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DazeSettingReader</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DazeSetting</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Daze@DazeSetting.xlsx</t>
         </is>
       </c>
     </row>
